--- a/data/trans_bre/IMC_inf_MED_R2-Dificultad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Dificultad-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-6.196765945138022</v>
+        <v>-5.355018631034519</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-11.72506234085981</v>
+        <v>-11.46839782438029</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-28.78806049418626</v>
+        <v>-24.14600830980924</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.1129563017898875</v>
+        <v>-0.0992678619723904</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.2438654716428404</v>
+        <v>-0.2456183482281183</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.5273218582094552</v>
+        <v>-0.4506358132931272</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-15.93255937706062</v>
+        <v>-13.83315951230163</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-19.75968042657534</v>
+        <v>-18.29566159721496</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-46.95945438457944</v>
+        <v>-42.20941046086602</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.2682753243476974</v>
+        <v>-0.2451030057897639</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.3838608470512054</v>
+        <v>-0.3689820185551875</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.7428687817143143</v>
+        <v>-0.6944193023361798</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2.897495375374999</v>
+        <v>2.16981182251755</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-3.229776233193715</v>
+        <v>-3.690549854252455</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-6.912146313358769</v>
+        <v>-4.123323033216622</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.05697372892734707</v>
+        <v>0.04271236411850009</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.07316873271008201</v>
+        <v>-0.07978854136743627</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.1578840085016966</v>
+        <v>-0.09698387272395363</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-13.69393939183359</v>
+        <v>-11.7720395336713</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-7.212768413268539</v>
+        <v>-8.951593748947563</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-7.106414273448042</v>
+        <v>-7.675879959959159</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2361165907026464</v>
+        <v>-0.2142003517228802</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.1713028391836278</v>
+        <v>-0.2052208916819789</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.1859594170134483</v>
+        <v>-0.2025920556217956</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-22.99242819743442</v>
+        <v>-20.0902536741255</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-17.30506951967519</v>
+        <v>-17.6446684216077</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-21.28143044536468</v>
+        <v>-22.11277556993502</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.3675873402685438</v>
+        <v>-0.3449579034173339</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3650805881298483</v>
+        <v>-0.3750459269884459</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.4753485486394497</v>
+        <v>-0.4813502109998806</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-4.961576625943493</v>
+        <v>-3.443162862909807</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1.847085346500827</v>
+        <v>-0.4706741412922981</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>7.631408240375369</v>
+        <v>6.269652005196537</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.08840487877157975</v>
+        <v>-0.06999890175282802</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.06296963930700396</v>
+        <v>-0.01327510594644816</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2450958876747415</v>
+        <v>0.2288194178521343</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-10.40965609920134</v>
+        <v>-7.168291492451112</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-9.272674534885633</v>
+        <v>-10.50412642145408</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-15.84412130893993</v>
+        <v>-15.4232342768274</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.214182518227694</v>
+        <v>-0.1553152904630339</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.209843914172474</v>
+        <v>-0.2367882822171812</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.3630135645782121</v>
+        <v>-0.347765446929223</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-21.16285125654442</v>
+        <v>-18.05826030764056</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-19.63161137860467</v>
+        <v>-20.06677277516077</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-28.09716409823098</v>
+        <v>-26.4429633252666</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.3903611840473312</v>
+        <v>-0.360434882768776</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.402520515771534</v>
+        <v>-0.4052334547329765</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.5633312263704733</v>
+        <v>-0.5300820966434329</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1.138310492892461</v>
+        <v>1.847918292631664</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2.138599660635573</v>
+        <v>-0.4359769925964623</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-3.849186948899274</v>
+        <v>-2.118386569294791</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.02972862103172552</v>
+        <v>0.03525869695657909</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.05366273378224055</v>
+        <v>0.0007829741638664175</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.09898843807023919</v>
+        <v>-0.05704911106919567</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2.775072259256028</v>
+        <v>1.659269525491336</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-15.43998469221956</v>
+        <v>-12.01898067840844</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-4.114465258879424</v>
+        <v>-3.056752969887577</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.06086276202908667</v>
+        <v>0.03473423081700941</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.3364900147026478</v>
+        <v>-0.278652039459935</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.1377842832947391</v>
+        <v>-0.1034674948025726</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-12.58815349936348</v>
+        <v>-12.20928613920579</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-29.12050286187063</v>
+        <v>-25.572668482</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-19.63758071971235</v>
+        <v>-18.86674177665817</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.2360696194785415</v>
+        <v>-0.2237588107745208</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5821754376344921</v>
+        <v>-0.5341829037522805</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.5101422111916363</v>
+        <v>-0.477738534081489</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>17.12479110376298</v>
+        <v>16.97644252482737</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.009374172376899324</v>
+        <v>0.9342911232007298</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>9.398908215671643</v>
+        <v>9.753583407443479</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.4717144479181342</v>
+        <v>0.4254328551416711</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.001446382919091199</v>
+        <v>0.02129262585346152</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.4368830167869366</v>
+        <v>0.4393994560682886</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-8.425320240984579</v>
+        <v>-6.914330774497518</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-10.31812554279518</v>
+        <v>-10.59830333388282</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-12.7938534078594</v>
+        <v>-11.98178517062588</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.1578888562687267</v>
+        <v>-0.1336559003140064</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.2278532493938309</v>
+        <v>-0.2359721851018638</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.3133222528607059</v>
+        <v>-0.2934803579304871</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-13.79540447338447</v>
+        <v>-11.8103681414187</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-15.00942027323213</v>
+        <v>-15.25388157566249</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-19.77912523518063</v>
+        <v>-18.78385849735006</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.245709143789574</v>
+        <v>-0.2187208457873439</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.3166662189767852</v>
+        <v>-0.3214411209893984</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.4469450647712847</v>
+        <v>-0.4294156329989147</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-3.422034191565542</v>
+        <v>-1.92904872451506</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-4.979053010337483</v>
+        <v>-5.93847175200399</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-5.931750436645789</v>
+        <v>-4.661583197898124</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.06729305829872645</v>
+        <v>-0.04043220170566302</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1156060490829998</v>
+        <v>-0.1386154766110995</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.1547552930843568</v>
+        <v>-0.1247734483657332</v>
       </c>
     </row>
     <row r="19">
